--- a/Result/profitability/3511.xlsx
+++ b/Result/profitability/3511.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,7 +668,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>15.8525</v>
+        <v>15.8075</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -777,7 +777,7 @@
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>18.3375</v>
+        <v>18.11625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -890,7 +890,7 @@
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>20.06625</v>
+        <v>19.98625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>22.5</v>
+        <v>22.6925</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>24.81</v>
+        <v>25.22125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>27.315</v>
+        <v>27.01</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>29.44875</v>
+        <v>29.0025</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9800,6 +9800,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3511</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>464</v>
+      </c>
+      <c r="D75" t="n">
+        <v>404</v>
+      </c>
+      <c r="E75" t="n">
+        <v>60</v>
+      </c>
+      <c r="F75" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-31</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-6.71%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-32</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-26</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.2262500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>13.33375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.57</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.2175502742230347</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.07999999999999996</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.1951219512195121</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.539999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1362831858407079</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
